--- a/informes_data/Segunda FEB/2025-26/Regular_Season/individual/NP_play_by_play_2486918_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Segunda FEB/2025-26/Regular_Season/individual/NP_play_by_play_2486918_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>3.4982</v>
+        <v>4.6956</v>
       </c>
       <c r="E2" t="n">
-        <v>0.9361</v>
+        <v>1.6296</v>
       </c>
       <c r="F2" t="n">
-        <v>2.5622</v>
+        <v>3.0661</v>
       </c>
       <c r="G2" t="n">
         <v>4.9827</v>
@@ -610,13 +610,13 @@
         <v>2.2588</v>
       </c>
       <c r="S2" t="n">
-        <v>-0.6676</v>
+        <v>0.5298</v>
       </c>
       <c r="T2" t="n">
-        <v>-0.8409</v>
+        <v>-0.1474</v>
       </c>
       <c r="U2" t="n">
-        <v>0.1733</v>
+        <v>0.6772</v>
       </c>
       <c r="V2" t="n">
         <v>0.0045</v>
@@ -643,13 +643,13 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>2.1102</v>
+        <v>2.4833</v>
       </c>
       <c r="E3" t="n">
-        <v>-1.1072</v>
+        <v>-0.7934</v>
       </c>
       <c r="F3" t="n">
-        <v>3.2175</v>
+        <v>3.2768</v>
       </c>
       <c r="G3" t="n">
         <v>3.3036</v>
@@ -688,13 +688,13 @@
         <v>1.4374</v>
       </c>
       <c r="S3" t="n">
-        <v>-0.2122</v>
+        <v>0.1609</v>
       </c>
       <c r="T3" t="n">
-        <v>-0.5851</v>
+        <v>-0.2713</v>
       </c>
       <c r="U3" t="n">
-        <v>0.3729</v>
+        <v>0.4322</v>
       </c>
       <c r="V3" t="n">
         <v>-1.3918</v>
@@ -709,7 +709,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>S. GALLEGO MOGRO</t>
+          <t>K. CLEMENT AIGBOGUN</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -721,73 +721,73 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>1.9219</v>
+        <v>1.139</v>
       </c>
       <c r="E4" t="n">
-        <v>1.6811</v>
+        <v>-1.9574</v>
       </c>
       <c r="F4" t="n">
-        <v>0.2408</v>
+        <v>3.0964</v>
       </c>
       <c r="G4" t="n">
-        <v>0.8704</v>
+        <v>2.1195</v>
       </c>
       <c r="H4" t="n">
-        <v>0.4573</v>
+        <v>1.1643</v>
       </c>
       <c r="I4" t="n">
-        <v>0.4131</v>
+        <v>0.9552</v>
       </c>
       <c r="J4" t="n">
-        <v>1.3326</v>
+        <v>0.4138</v>
       </c>
       <c r="K4" t="n">
-        <v>0.8988</v>
+        <v>0.9928</v>
       </c>
       <c r="L4" t="n">
-        <v>0.4338</v>
+        <v>-0.579</v>
       </c>
       <c r="M4" t="n">
-        <v>-0.4622</v>
+        <v>1.7057</v>
       </c>
       <c r="N4" t="n">
-        <v>-0.4415</v>
+        <v>0.1716</v>
       </c>
       <c r="O4" t="n">
-        <v>-0.0207</v>
+        <v>1.5342</v>
       </c>
       <c r="P4" t="n">
-        <v>-0.2053</v>
+        <v>-0.616</v>
       </c>
       <c r="Q4" t="n">
-        <v>-1.0267</v>
+        <v>-2.0534</v>
       </c>
       <c r="R4" t="n">
-        <v>0.8214</v>
+        <v>1.4374</v>
       </c>
       <c r="S4" t="n">
-        <v>2.0864</v>
+        <v>0.3517</v>
       </c>
       <c r="T4" t="n">
-        <v>1.3752</v>
+        <v>-0.3178</v>
       </c>
       <c r="U4" t="n">
-        <v>0.7112000000000001</v>
+        <v>0.6695</v>
       </c>
       <c r="V4" t="n">
-        <v>-0.8295</v>
+        <v>-0.7161999999999999</v>
       </c>
       <c r="W4" t="n">
         <v>0</v>
       </c>
       <c r="X4" t="n">
-        <v>-0.8295</v>
+        <v>-0.7161999999999999</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>K. CLEMENT AIGBOGUN</t>
+          <t>S. GALLEGO MOGRO</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,73 +799,73 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>1.3745</v>
+        <v>1.0414</v>
       </c>
       <c r="E5" t="n">
-        <v>-2.1666</v>
+        <v>0.9489</v>
       </c>
       <c r="F5" t="n">
-        <v>3.5411</v>
+        <v>0.0926</v>
       </c>
       <c r="G5" t="n">
-        <v>2.1195</v>
+        <v>0.8704</v>
       </c>
       <c r="H5" t="n">
-        <v>1.1643</v>
+        <v>0.4573</v>
       </c>
       <c r="I5" t="n">
-        <v>0.9552</v>
+        <v>0.4131</v>
       </c>
       <c r="J5" t="n">
-        <v>0.4138</v>
+        <v>1.3326</v>
       </c>
       <c r="K5" t="n">
-        <v>0.9928</v>
+        <v>0.8988</v>
       </c>
       <c r="L5" t="n">
-        <v>-0.579</v>
+        <v>0.4338</v>
       </c>
       <c r="M5" t="n">
-        <v>1.7057</v>
+        <v>-0.4622</v>
       </c>
       <c r="N5" t="n">
-        <v>0.1716</v>
+        <v>-0.4415</v>
       </c>
       <c r="O5" t="n">
-        <v>1.5342</v>
+        <v>-0.0207</v>
       </c>
       <c r="P5" t="n">
-        <v>-0.616</v>
+        <v>-0.2053</v>
       </c>
       <c r="Q5" t="n">
-        <v>-2.0534</v>
+        <v>-1.0267</v>
       </c>
       <c r="R5" t="n">
-        <v>1.4374</v>
+        <v>0.8214</v>
       </c>
       <c r="S5" t="n">
-        <v>0.5872000000000001</v>
+        <v>1.2059</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.527</v>
+        <v>0.643</v>
       </c>
       <c r="U5" t="n">
-        <v>1.1141</v>
+        <v>0.5629999999999999</v>
       </c>
       <c r="V5" t="n">
-        <v>-0.7161999999999999</v>
+        <v>-0.8295</v>
       </c>
       <c r="W5" t="n">
         <v>0</v>
       </c>
       <c r="X5" t="n">
-        <v>-0.7161999999999999</v>
+        <v>-0.8295</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>D. KANDULU</t>
+          <t>D. RIVAS PALMER</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,73 +877,73 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>1.1701</v>
+        <v>1.0271</v>
       </c>
       <c r="E6" t="n">
-        <v>-1.3375</v>
+        <v>-1.4477</v>
       </c>
       <c r="F6" t="n">
-        <v>2.5076</v>
+        <v>2.4748</v>
       </c>
       <c r="G6" t="n">
-        <v>-0.8581</v>
+        <v>-0.7674</v>
       </c>
       <c r="H6" t="n">
-        <v>-1.0477</v>
+        <v>-2.9618</v>
       </c>
       <c r="I6" t="n">
-        <v>0.1897</v>
+        <v>2.1944</v>
       </c>
       <c r="J6" t="n">
-        <v>-0.2641</v>
+        <v>-1.4631</v>
       </c>
       <c r="K6" t="n">
-        <v>-0.3825</v>
+        <v>-2.6337</v>
       </c>
       <c r="L6" t="n">
-        <v>0.1184</v>
+        <v>1.1706</v>
       </c>
       <c r="M6" t="n">
-        <v>-0.594</v>
+        <v>0.6957</v>
       </c>
       <c r="N6" t="n">
-        <v>-0.6653</v>
+        <v>-0.3281</v>
       </c>
       <c r="O6" t="n">
-        <v>0.0713</v>
+        <v>1.0238</v>
       </c>
       <c r="P6" t="n">
-        <v>-1.4374</v>
+        <v>0.8214</v>
       </c>
       <c r="Q6" t="n">
-        <v>-3.0801</v>
+        <v>-1.0267</v>
       </c>
       <c r="R6" t="n">
-        <v>1.6427</v>
+        <v>1.8481</v>
       </c>
       <c r="S6" t="n">
-        <v>2.7674</v>
+        <v>0.7285</v>
       </c>
       <c r="T6" t="n">
-        <v>2.0067</v>
+        <v>0.3214</v>
       </c>
       <c r="U6" t="n">
-        <v>0.7607</v>
+        <v>0.407</v>
       </c>
       <c r="V6" t="n">
-        <v>0.6982</v>
+        <v>0.2447</v>
       </c>
       <c r="W6" t="n">
-        <v>0</v>
+        <v>0.7207</v>
       </c>
       <c r="X6" t="n">
-        <v>0.6982</v>
+        <v>-0.476</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>D. RIVAS PALMER</t>
+          <t>V. PEREZ TOMAS</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,73 +955,73 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>0.7521</v>
+        <v>0.49</v>
       </c>
       <c r="E7" t="n">
-        <v>-1.7228</v>
+        <v>-1.0633</v>
       </c>
       <c r="F7" t="n">
-        <v>2.4748</v>
+        <v>1.5533</v>
       </c>
       <c r="G7" t="n">
-        <v>-0.7674</v>
+        <v>0.8354</v>
       </c>
       <c r="H7" t="n">
-        <v>-2.9618</v>
+        <v>1.0512</v>
       </c>
       <c r="I7" t="n">
-        <v>2.1944</v>
+        <v>-0.2157</v>
       </c>
       <c r="J7" t="n">
-        <v>-1.4631</v>
+        <v>0.4745</v>
       </c>
       <c r="K7" t="n">
-        <v>-2.6337</v>
+        <v>1.1324</v>
       </c>
       <c r="L7" t="n">
-        <v>1.1706</v>
+        <v>-0.6579</v>
       </c>
       <c r="M7" t="n">
-        <v>0.6957</v>
+        <v>0.3609</v>
       </c>
       <c r="N7" t="n">
-        <v>-0.3281</v>
+        <v>-0.0813</v>
       </c>
       <c r="O7" t="n">
-        <v>1.0238</v>
+        <v>0.4422</v>
       </c>
       <c r="P7" t="n">
-        <v>0.8214</v>
+        <v>-1.0267</v>
       </c>
       <c r="Q7" t="n">
-        <v>-1.0267</v>
+        <v>-2.0534</v>
       </c>
       <c r="R7" t="n">
-        <v>1.8481</v>
+        <v>1.0267</v>
       </c>
       <c r="S7" t="n">
-        <v>0.4534</v>
+        <v>0.092</v>
       </c>
       <c r="T7" t="n">
-        <v>0.0464</v>
+        <v>-0.0737</v>
       </c>
       <c r="U7" t="n">
-        <v>0.407</v>
+        <v>0.1657</v>
       </c>
       <c r="V7" t="n">
-        <v>0.2447</v>
+        <v>0.5893</v>
       </c>
       <c r="W7" t="n">
-        <v>0.7207</v>
+        <v>0.5893</v>
       </c>
       <c r="X7" t="n">
-        <v>-0.476</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>H. SALOMON</t>
+          <t>E. HERRERA SAURET</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,73 +1033,73 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>0.0573</v>
+        <v>0.4681</v>
       </c>
       <c r="E8" t="n">
-        <v>-1.7503</v>
+        <v>2.1843</v>
       </c>
       <c r="F8" t="n">
-        <v>1.8076</v>
+        <v>-1.7163</v>
       </c>
       <c r="G8" t="n">
-        <v>-0.6784</v>
+        <v>1.4106</v>
       </c>
       <c r="H8" t="n">
-        <v>-1.7256</v>
+        <v>0.824</v>
       </c>
       <c r="I8" t="n">
-        <v>1.0472</v>
+        <v>0.5866</v>
       </c>
       <c r="J8" t="n">
-        <v>-1.4286</v>
+        <v>0.9387</v>
       </c>
       <c r="K8" t="n">
-        <v>-2.0337</v>
+        <v>1.0969</v>
       </c>
       <c r="L8" t="n">
-        <v>0.605</v>
+        <v>-0.1582</v>
       </c>
       <c r="M8" t="n">
-        <v>0.7502</v>
+        <v>0.4719</v>
       </c>
       <c r="N8" t="n">
-        <v>0.308</v>
+        <v>-0.2729</v>
       </c>
       <c r="O8" t="n">
-        <v>0.4422</v>
+        <v>0.7449</v>
       </c>
       <c r="P8" t="n">
-        <v>1.2321</v>
+        <v>-0.616</v>
       </c>
       <c r="Q8" t="n">
-        <v>0</v>
+        <v>-2.0534</v>
       </c>
       <c r="R8" t="n">
-        <v>1.2321</v>
+        <v>1.4374</v>
       </c>
       <c r="S8" t="n">
-        <v>-0.4963</v>
+        <v>0.8476</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.3216</v>
+        <v>0.1122</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.1747</v>
+        <v>0.7354000000000001</v>
       </c>
       <c r="V8" t="n">
-        <v>0</v>
+        <v>-1.1741</v>
       </c>
       <c r="W8" t="n">
-        <v>0</v>
+        <v>3.1868</v>
       </c>
       <c r="X8" t="n">
-        <v>0</v>
+        <v>-4.3609</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>V. PEREZ TOMAS</t>
+          <t>H. SALOMON</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,64 +1111,64 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-0.1564</v>
+        <v>0.4287</v>
       </c>
       <c r="E9" t="n">
-        <v>-1.4429</v>
+        <v>-1.6457</v>
       </c>
       <c r="F9" t="n">
-        <v>1.2865</v>
+        <v>2.0743</v>
       </c>
       <c r="G9" t="n">
-        <v>0.8354</v>
+        <v>-0.6784</v>
       </c>
       <c r="H9" t="n">
-        <v>1.0512</v>
+        <v>-1.7256</v>
       </c>
       <c r="I9" t="n">
-        <v>-0.2157</v>
+        <v>1.0472</v>
       </c>
       <c r="J9" t="n">
-        <v>0.4745</v>
+        <v>-1.4286</v>
       </c>
       <c r="K9" t="n">
-        <v>1.1324</v>
+        <v>-2.0337</v>
       </c>
       <c r="L9" t="n">
-        <v>-0.6579</v>
+        <v>0.605</v>
       </c>
       <c r="M9" t="n">
-        <v>0.3609</v>
+        <v>0.7502</v>
       </c>
       <c r="N9" t="n">
-        <v>-0.0813</v>
+        <v>0.308</v>
       </c>
       <c r="O9" t="n">
         <v>0.4422</v>
       </c>
       <c r="P9" t="n">
-        <v>-1.0267</v>
+        <v>1.2321</v>
       </c>
       <c r="Q9" t="n">
-        <v>-2.0534</v>
+        <v>0</v>
       </c>
       <c r="R9" t="n">
-        <v>1.0267</v>
+        <v>1.2321</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.5545</v>
+        <v>-0.1249</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.4534</v>
+        <v>-0.217</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.1011</v>
+        <v>0.0921</v>
       </c>
       <c r="V9" t="n">
-        <v>0.5893</v>
+        <v>0</v>
       </c>
       <c r="W9" t="n">
-        <v>0.5893</v>
+        <v>0</v>
       </c>
       <c r="X9" t="n">
         <v>0</v>
@@ -1177,7 +1177,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>E. HERRERA SAURET</t>
+          <t>D. KANDULU</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1189,67 +1189,67 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-0.1613</v>
+        <v>-0.2268</v>
       </c>
       <c r="E10" t="n">
-        <v>1.3475</v>
+        <v>-2.5269</v>
       </c>
       <c r="F10" t="n">
-        <v>-1.5088</v>
+        <v>2.3001</v>
       </c>
       <c r="G10" t="n">
-        <v>1.4106</v>
+        <v>-0.8581</v>
       </c>
       <c r="H10" t="n">
-        <v>0.824</v>
+        <v>-1.0477</v>
       </c>
       <c r="I10" t="n">
-        <v>0.5866</v>
+        <v>0.1897</v>
       </c>
       <c r="J10" t="n">
-        <v>0.9387</v>
+        <v>-0.2641</v>
       </c>
       <c r="K10" t="n">
-        <v>1.0969</v>
+        <v>-0.3825</v>
       </c>
       <c r="L10" t="n">
-        <v>-0.1582</v>
+        <v>0.1184</v>
       </c>
       <c r="M10" t="n">
-        <v>0.4719</v>
+        <v>-0.594</v>
       </c>
       <c r="N10" t="n">
-        <v>-0.2729</v>
+        <v>-0.6653</v>
       </c>
       <c r="O10" t="n">
-        <v>0.7449</v>
+        <v>0.0713</v>
       </c>
       <c r="P10" t="n">
-        <v>-0.616</v>
+        <v>-1.4374</v>
       </c>
       <c r="Q10" t="n">
-        <v>-2.0534</v>
+        <v>-3.0801</v>
       </c>
       <c r="R10" t="n">
-        <v>1.4374</v>
+        <v>1.6427</v>
       </c>
       <c r="S10" t="n">
-        <v>0.2183</v>
+        <v>1.3705</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.7246</v>
+        <v>0.8173</v>
       </c>
       <c r="U10" t="n">
-        <v>0.9429</v>
+        <v>0.5532</v>
       </c>
       <c r="V10" t="n">
-        <v>-1.1741</v>
+        <v>0.6982</v>
       </c>
       <c r="W10" t="n">
-        <v>3.1868</v>
+        <v>0</v>
       </c>
       <c r="X10" t="n">
-        <v>-4.3609</v>
+        <v>0.6982</v>
       </c>
     </row>
     <row r="11">
@@ -1267,13 +1267,13 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-0.9046</v>
+        <v>-1.1212</v>
       </c>
       <c r="E11" t="n">
-        <v>0.5119</v>
+        <v>0.4731</v>
       </c>
       <c r="F11" t="n">
-        <v>-1.4165</v>
+        <v>-1.5943</v>
       </c>
       <c r="G11" t="n">
         <v>-0.6686</v>
@@ -1312,13 +1312,13 @@
         <v>0.8214</v>
       </c>
       <c r="S11" t="n">
-        <v>0.7105</v>
+        <v>0.4939</v>
       </c>
       <c r="T11" t="n">
-        <v>0.3098</v>
+        <v>0.2711</v>
       </c>
       <c r="U11" t="n">
-        <v>0.4007</v>
+        <v>0.2228</v>
       </c>
       <c r="V11" t="n">
         <v>-1.7679</v>
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-1.4257</v>
+        <v>-1.8597</v>
       </c>
       <c r="E12" t="n">
-        <v>-2.6826</v>
+        <v>-3.2056</v>
       </c>
       <c r="F12" t="n">
-        <v>1.2569</v>
+        <v>1.3459</v>
       </c>
       <c r="G12" t="n">
         <v>0.3971</v>
@@ -1390,13 +1390,13 @@
         <v>1.4374</v>
       </c>
       <c r="S12" t="n">
-        <v>0.4545</v>
+        <v>0.0204</v>
       </c>
       <c r="T12" t="n">
-        <v>0.8754999999999999</v>
+        <v>0.3524</v>
       </c>
       <c r="U12" t="n">
-        <v>-0.4209</v>
+        <v>-0.332</v>
       </c>
       <c r="V12" t="n">
         <v>1.4189</v>
@@ -1423,10 +1423,10 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>8.2363</v>
+        <v>8.565499999999998</v>
       </c>
       <c r="E13" t="n">
-        <v>-7.7333</v>
+        <v>-7.4041</v>
       </c>
       <c r="F13" t="n">
         <v>15.9697</v>
@@ -1435,7 +1435,7 @@
         <v>10.9468</v>
       </c>
       <c r="H13" t="n">
-        <v>-0.5518000000000005</v>
+        <v>-0.5518000000000004</v>
       </c>
       <c r="I13" t="n">
         <v>11.4987</v>
@@ -1447,7 +1447,7 @@
         <v>1.771</v>
       </c>
       <c r="L13" t="n">
-        <v>4.6287</v>
+        <v>4.628700000000001</v>
       </c>
       <c r="M13" t="n">
         <v>4.547099999999999</v>
@@ -1468,13 +1468,13 @@
         <v>15.4008</v>
       </c>
       <c r="S13" t="n">
-        <v>5.3471</v>
+        <v>5.6763</v>
       </c>
       <c r="T13" t="n">
-        <v>1.161</v>
+        <v>1.4902</v>
       </c>
       <c r="U13" t="n">
-        <v>4.1861</v>
+        <v>4.186100000000001</v>
       </c>
       <c r="V13" t="n">
         <v>-2.9239</v>
@@ -1501,13 +1501,13 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>4.165</v>
+        <v>3.2149</v>
       </c>
       <c r="E14" t="n">
-        <v>0.5268</v>
+        <v>-0.4146</v>
       </c>
       <c r="F14" t="n">
-        <v>3.6382</v>
+        <v>3.6294</v>
       </c>
       <c r="G14" t="n">
         <v>-0.4326</v>
@@ -1546,13 +1546,13 @@
         <v>2.8748</v>
       </c>
       <c r="S14" t="n">
-        <v>1.23</v>
+        <v>0.2799</v>
       </c>
       <c r="T14" t="n">
-        <v>1.0613</v>
+        <v>0.1199</v>
       </c>
       <c r="U14" t="n">
-        <v>0.1687</v>
+        <v>0.16</v>
       </c>
       <c r="V14" t="n">
         <v>0.6982</v>
@@ -1579,13 +1579,13 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>2.8469</v>
+        <v>2.7754</v>
       </c>
       <c r="E15" t="n">
-        <v>0.232</v>
+        <v>0.5458</v>
       </c>
       <c r="F15" t="n">
-        <v>2.6149</v>
+        <v>2.2295</v>
       </c>
       <c r="G15" t="n">
         <v>2.2013</v>
@@ -1624,13 +1624,13 @@
         <v>1.6427</v>
       </c>
       <c r="S15" t="n">
-        <v>-0.4427</v>
+        <v>-0.5143</v>
       </c>
       <c r="T15" t="n">
-        <v>-0.7169</v>
+        <v>-0.4031</v>
       </c>
       <c r="U15" t="n">
-        <v>0.2741</v>
+        <v>-0.1112</v>
       </c>
       <c r="V15" t="n">
         <v>-0.3491</v>
@@ -1645,7 +1645,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>G. MILADINOVIC</t>
+          <t>J. TAVELLI</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1657,40 +1657,40 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>-0.2471</v>
+        <v>-0.6329</v>
       </c>
       <c r="E16" t="n">
-        <v>-1.5987</v>
+        <v>-1.4581</v>
       </c>
       <c r="F16" t="n">
-        <v>1.3516</v>
+        <v>0.8252</v>
       </c>
       <c r="G16" t="n">
-        <v>0.4155</v>
+        <v>-1.131</v>
       </c>
       <c r="H16" t="n">
-        <v>-0.3082</v>
+        <v>-1.3072</v>
       </c>
       <c r="I16" t="n">
-        <v>0.7238</v>
+        <v>0.1763</v>
       </c>
       <c r="J16" t="n">
-        <v>0.0279</v>
+        <v>-0.5607</v>
       </c>
       <c r="K16" t="n">
-        <v>-0.0905</v>
+        <v>-1.0604</v>
       </c>
       <c r="L16" t="n">
-        <v>0.1184</v>
+        <v>0.4997</v>
       </c>
       <c r="M16" t="n">
-        <v>0.3876</v>
+        <v>-0.5702</v>
       </c>
       <c r="N16" t="n">
-        <v>-0.2177</v>
+        <v>-0.2468</v>
       </c>
       <c r="O16" t="n">
-        <v>0.6054</v>
+        <v>-0.3234</v>
       </c>
       <c r="P16" t="n">
         <v>-0</v>
@@ -1702,22 +1702,22 @@
         <v>2.4641</v>
       </c>
       <c r="S16" t="n">
-        <v>-0.1867</v>
+        <v>-0.9028</v>
       </c>
       <c r="T16" t="n">
-        <v>-0.3411</v>
+        <v>-0.7906</v>
       </c>
       <c r="U16" t="n">
-        <v>0.1544</v>
+        <v>-0.1122</v>
       </c>
       <c r="V16" t="n">
-        <v>-0.476</v>
+        <v>1.4008</v>
       </c>
       <c r="W16" t="n">
-        <v>1.1786</v>
+        <v>2.3573</v>
       </c>
       <c r="X16" t="n">
-        <v>-1.6546</v>
+        <v>-0.9564</v>
       </c>
     </row>
     <row r="17">
@@ -1735,13 +1735,13 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>-0.629</v>
+        <v>-0.7248</v>
       </c>
       <c r="E17" t="n">
-        <v>-0.0598</v>
+        <v>-0.5828</v>
       </c>
       <c r="F17" t="n">
-        <v>-0.5692</v>
+        <v>-0.142</v>
       </c>
       <c r="G17" t="n">
         <v>-0.2937</v>
@@ -1780,13 +1780,13 @@
         <v>1.6427</v>
       </c>
       <c r="S17" t="n">
-        <v>0.5558999999999999</v>
+        <v>0.46</v>
       </c>
       <c r="T17" t="n">
-        <v>0.6197</v>
+        <v>0.09669999999999999</v>
       </c>
       <c r="U17" t="n">
-        <v>-0.0638</v>
+        <v>0.3633</v>
       </c>
       <c r="V17" t="n">
         <v>-0.4805</v>
@@ -1801,7 +1801,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>R. MARTÍNEZ-QUINTANILLA JIMÉNEZ</t>
+          <t>G. MILADINOVIC</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,73 +1813,73 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-1.1467</v>
+        <v>-0.9167</v>
       </c>
       <c r="E18" t="n">
-        <v>-1.0808</v>
+        <v>-1.9125</v>
       </c>
       <c r="F18" t="n">
-        <v>-0.0658</v>
+        <v>0.9959</v>
       </c>
       <c r="G18" t="n">
-        <v>-0.7331</v>
+        <v>0.4155</v>
       </c>
       <c r="H18" t="n">
-        <v>-0.0357</v>
+        <v>-0.3082</v>
       </c>
       <c r="I18" t="n">
-        <v>-0.6974</v>
+        <v>0.7238</v>
       </c>
       <c r="J18" t="n">
-        <v>-0.6778999999999999</v>
+        <v>0.0279</v>
       </c>
       <c r="K18" t="n">
-        <v>0.0195</v>
+        <v>-0.0905</v>
       </c>
       <c r="L18" t="n">
-        <v>-0.6974</v>
+        <v>0.1184</v>
       </c>
       <c r="M18" t="n">
-        <v>-0.0552</v>
+        <v>0.3876</v>
       </c>
       <c r="N18" t="n">
-        <v>-0.0552</v>
+        <v>-0.2177</v>
       </c>
       <c r="O18" t="n">
-        <v>0</v>
+        <v>0.6054</v>
       </c>
       <c r="P18" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="Q18" t="n">
-        <v>-0.2053</v>
+        <v>-2.4641</v>
       </c>
       <c r="R18" t="n">
-        <v>0.2053</v>
+        <v>2.4641</v>
       </c>
       <c r="S18" t="n">
-        <v>-0.1779</v>
+        <v>-0.8562</v>
       </c>
       <c r="T18" t="n">
-        <v>-0.1976</v>
+        <v>-0.655</v>
       </c>
       <c r="U18" t="n">
-        <v>0.0198</v>
+        <v>-0.2013</v>
       </c>
       <c r="V18" t="n">
-        <v>-0.2357</v>
+        <v>-0.476</v>
       </c>
       <c r="W18" t="n">
-        <v>0</v>
+        <v>1.1786</v>
       </c>
       <c r="X18" t="n">
-        <v>-0.2357</v>
+        <v>-1.6546</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>J. TAVELLI</t>
+          <t>R. MARTÍNEZ-QUINTANILLA JIMÉNEZ</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,67 +1891,67 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-1.1839</v>
+        <v>-1.117</v>
       </c>
       <c r="E19" t="n">
-        <v>-1.7719</v>
+        <v>-1.0808</v>
       </c>
       <c r="F19" t="n">
-        <v>0.5881</v>
+        <v>-0.0362</v>
       </c>
       <c r="G19" t="n">
-        <v>-1.131</v>
+        <v>-0.7331</v>
       </c>
       <c r="H19" t="n">
-        <v>-1.3072</v>
+        <v>-0.0357</v>
       </c>
       <c r="I19" t="n">
-        <v>0.1763</v>
+        <v>-0.6974</v>
       </c>
       <c r="J19" t="n">
-        <v>-0.5607</v>
+        <v>-0.6778999999999999</v>
       </c>
       <c r="K19" t="n">
-        <v>-1.0604</v>
+        <v>0.0195</v>
       </c>
       <c r="L19" t="n">
-        <v>0.4997</v>
+        <v>-0.6974</v>
       </c>
       <c r="M19" t="n">
-        <v>-0.5702</v>
+        <v>-0.0552</v>
       </c>
       <c r="N19" t="n">
-        <v>-0.2468</v>
+        <v>-0.0552</v>
       </c>
       <c r="O19" t="n">
-        <v>-0.3234</v>
+        <v>0</v>
       </c>
       <c r="P19" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Q19" t="n">
-        <v>-2.4641</v>
+        <v>-0.2053</v>
       </c>
       <c r="R19" t="n">
-        <v>2.4641</v>
+        <v>0.2053</v>
       </c>
       <c r="S19" t="n">
-        <v>-1.4537</v>
+        <v>-0.1482</v>
       </c>
       <c r="T19" t="n">
-        <v>-1.1044</v>
+        <v>-0.1976</v>
       </c>
       <c r="U19" t="n">
-        <v>-0.3494</v>
+        <v>0.0494</v>
       </c>
       <c r="V19" t="n">
-        <v>1.4008</v>
+        <v>-0.2357</v>
       </c>
       <c r="W19" t="n">
-        <v>2.3573</v>
+        <v>0</v>
       </c>
       <c r="X19" t="n">
-        <v>-0.9564</v>
+        <v>-0.2357</v>
       </c>
     </row>
     <row r="20">
@@ -1969,13 +1969,13 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-1.929</v>
+        <v>-1.5577</v>
       </c>
       <c r="E20" t="n">
-        <v>-3.1414</v>
+        <v>-2.723</v>
       </c>
       <c r="F20" t="n">
-        <v>1.2124</v>
+        <v>1.1653</v>
       </c>
       <c r="G20" t="n">
         <v>-3.3269</v>
@@ -2014,13 +2014,13 @@
         <v>2.4641</v>
       </c>
       <c r="S20" t="n">
-        <v>-0.7171</v>
+        <v>-0.3458</v>
       </c>
       <c r="T20" t="n">
-        <v>-1.0966</v>
+        <v>-0.6782</v>
       </c>
       <c r="U20" t="n">
-        <v>0.3795</v>
+        <v>0.3324</v>
       </c>
       <c r="V20" t="n">
         <v>-0.3491</v>
@@ -2047,13 +2047,13 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-2.7831</v>
+        <v>-2.2566</v>
       </c>
       <c r="E21" t="n">
-        <v>-2.6393</v>
+        <v>-2.4301</v>
       </c>
       <c r="F21" t="n">
-        <v>-0.1438</v>
+        <v>0.1735</v>
       </c>
       <c r="G21" t="n">
         <v>-0.3959</v>
@@ -2092,13 +2092,13 @@
         <v>2.0534</v>
       </c>
       <c r="S21" t="n">
-        <v>-1.5087</v>
+        <v>-0.9822</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.8409</v>
+        <v>-0.6317</v>
       </c>
       <c r="U21" t="n">
-        <v>-0.6677999999999999</v>
+        <v>-0.3505</v>
       </c>
       <c r="V21" t="n">
         <v>0.3536</v>
@@ -2125,13 +2125,13 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-3.3208</v>
+        <v>-2.4927</v>
       </c>
       <c r="E22" t="n">
-        <v>-2.2163</v>
+        <v>-2.1117</v>
       </c>
       <c r="F22" t="n">
-        <v>-1.1046</v>
+        <v>-0.381</v>
       </c>
       <c r="G22" t="n">
         <v>-1.0902</v>
@@ -2170,13 +2170,13 @@
         <v>2.2588</v>
       </c>
       <c r="S22" t="n">
-        <v>-1.2922</v>
+        <v>-0.464</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.3993</v>
+        <v>-0.2947</v>
       </c>
       <c r="U22" t="n">
-        <v>-0.8929</v>
+        <v>-0.1694</v>
       </c>
       <c r="V22" t="n">
         <v>-0.9384</v>
@@ -2203,13 +2203,13 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-4.0086</v>
+        <v>-3.1334</v>
       </c>
       <c r="E23" t="n">
-        <v>-4.2203</v>
+        <v>-3.8018</v>
       </c>
       <c r="F23" t="n">
-        <v>0.2117</v>
+        <v>0.6685</v>
       </c>
       <c r="G23" t="n">
         <v>-6.1603</v>
@@ -2248,13 +2248,13 @@
         <v>2.4641</v>
       </c>
       <c r="S23" t="n">
-        <v>-1.3538</v>
+        <v>-0.4786</v>
       </c>
       <c r="T23" t="n">
-        <v>-1.1702</v>
+        <v>-0.7518</v>
       </c>
       <c r="U23" t="n">
-        <v>-0.1836</v>
+        <v>0.2732</v>
       </c>
       <c r="V23" t="n">
         <v>3.3002</v>
@@ -2281,13 +2281,13 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-8.2363</v>
+        <v>-6.841500000000001</v>
       </c>
       <c r="E24" t="n">
-        <v>-15.9697</v>
+        <v>-15.9696</v>
       </c>
       <c r="F24" t="n">
-        <v>7.733500000000001</v>
+        <v>9.1281</v>
       </c>
       <c r="G24" t="n">
         <v>-10.9469</v>
@@ -2326,13 +2326,13 @@
         <v>20.5341</v>
       </c>
       <c r="S24" t="n">
-        <v>-5.3469</v>
+        <v>-3.9522</v>
       </c>
       <c r="T24" t="n">
-        <v>-4.186</v>
+        <v>-4.186100000000001</v>
       </c>
       <c r="U24" t="n">
-        <v>-1.161</v>
+        <v>0.2337</v>
       </c>
       <c r="V24" t="n">
         <v>2.924</v>
